--- a/Perf/speedup/17fp_time.xlsx
+++ b/Perf/speedup/17fp_time.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84AED79-8B14-4514-84EB-35B263B3486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76255CC-0776-4B40-BC3C-73EA20E39D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>vm-small</t>
   </si>
@@ -78,6 +78,22 @@
   </si>
   <si>
     <t>549</t>
+  </si>
+  <si>
+    <t>Perf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perf error%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin error%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -162,6 +178,1077 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2017</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" baseline="0"/>
+              <a:t> FP</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$4:$N$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5.9569622411834224</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0772732703508971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.8896645965321399</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5454386636685495</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.1011312146117093E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2317706183030879</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.198445644028501</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5411505823416483</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.19528868772509242</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F54B-4640-87C5-A11EAEF8D307}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$4:$P$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.5636149636021256</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24939551408665128</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5300520657157455E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31809802522109326</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9873029302177725</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3982529465432485</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5915008725290738</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38226420129528077</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17178274620349041</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F54B-4640-87C5-A11EAEF8D307}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="325384383"/>
+        <c:axId val="325378143"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="325384383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="325378143"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="325378143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="325384383"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>77561</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>138793</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>77561</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0DD597D-EC91-BC52-F972-ACFEEE083345}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,10 +1536,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +1553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -499,7 +1586,7 @@
         <v>0.93047482117237845</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -531,8 +1618,20 @@
         <f t="shared" ref="I3:I12" si="3">AVERAGE(F3:H3)</f>
         <v>1.1426237340858239</v>
       </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -564,8 +1663,27 @@
         <f t="shared" si="3"/>
         <v>1.1371839283899405</v>
       </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(AVERAGE(I3,I9),AVERAGE(I2,I4:I8,I10:I12))</f>
+        <v>1.0538479464508104</v>
+      </c>
+      <c r="N4">
+        <f>100*ABS(M4-0.9946)/0.9946</f>
+        <v>5.9569622411834224</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGE(AVERAGE(I7,I9),AVERAGE(I2,I3,I4,I5,I6,I8,I10,I11,I12))</f>
+        <v>1.0002057144279868</v>
+      </c>
+      <c r="P4">
+        <f>100*ABS(O4-0.9946)/0.9946</f>
+        <v>0.5636149636021256</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -597,8 +1715,27 @@
         <f t="shared" si="3"/>
         <v>0.94312929416442959</v>
       </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(I3,I9,AVERAGE(I4:I8,I10:I12,I2))</f>
+        <v>1.0848825599469101</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N12" si="4">100*ABS(M5-0.9946)/0.9946</f>
+        <v>9.0772732703508971</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(AVERAGE(I7,I9),AVERAGE(I2,I3,I4,I6),AVERAGE(I5,I8,I10,I11,I12))</f>
+        <v>0.99708048778310587</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P12" si="5">100*ABS(O5-0.9946)/0.9946</f>
+        <v>0.24939551408665128</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -630,8 +1767,27 @@
         <f t="shared" si="3"/>
         <v>0.7439692466098845</v>
       </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(I3,I9,I7,AVERAGE(I4:I6,I8,I10:I12,I2))</f>
+        <v>1.0332866040771087</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>3.8896645965321399</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(AVERAGE(I7,I9),AVERAGE(I3,I6),AVERAGE(I2,I4),AVERAGE(I5,I8,I10,I11,I12))</f>
+        <v>0.99495109897845613</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>3.5300520657157455E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -663,8 +1819,27 @@
         <f t="shared" si="3"/>
         <v>0.86674939796844663</v>
       </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I4:I6,I10:I12,I2))</f>
+        <v>0.97922906705115265</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>1.5454386636685495</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(I7,I9,AVERAGE(I3,I6),AVERAGE(I2,I4),AVERAGE(I5,I8,I10,I11,I12))</f>
+        <v>0.99776380295884903</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>0.31809802522109326</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -696,8 +1871,27 @@
         <f t="shared" si="3"/>
         <v>0.72808316469492185</v>
       </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I4:I6,I10,I2),AVERAGE(I11:I12))</f>
+        <v>0.99379426148939476</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>8.1011312146117093E-2</v>
+      </c>
+      <c r="O8">
+        <f>AVERAGE(I7,I9,AVERAGE(I3,I6),AVERAGE(I2,I4),AVERAGE(I5,I8,I10,I11),I12)</f>
+        <v>1.014365714943946</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>1.9873029302177725</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -729,8 +1923,27 @@
         <f t="shared" si="3"/>
         <v>1.1512798397923951</v>
       </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I5,I10),AVERAGE(I2,I4,I6),AVERAGE(I11:I12))</f>
+        <v>0.99229480943035753</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>0.2317706183030879</v>
+      </c>
+      <c r="O9">
+        <f>AVERAGE(I7,I9,AVERAGE(I3,I6),AVERAGE(I2,I4),AVERAGE(I5,I8,I11),I10,I12)</f>
+        <v>1.0184530238063192</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>2.3982529465432485</v>
+      </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -762,8 +1975,27 @@
         <f t="shared" si="3"/>
         <v>1.084918586679483</v>
       </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I5,I10),AVERAGE(I2,I4,I6),I11,I12)</f>
+        <v>1.0065197403755075</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>1.198445644028501</v>
+      </c>
+      <c r="O10">
+        <f>AVERAGE(I7,I9,AVERAGE(I3,I6),I2,I4,AVERAGE(I5,I8,I11),I10,I12)</f>
+        <v>1.0203750676781742</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="5"/>
+        <v>2.5915008725290738</v>
+      </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -795,8 +2027,27 @@
         <f t="shared" si="3"/>
         <v>1.0802427847920042</v>
       </c>
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I5,I10),AVERAGE(I2,I6),I4,I11,I12)</f>
+        <v>1.0099282836919701</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="4"/>
+        <v>1.5411505823416483</v>
+      </c>
+      <c r="O11">
+        <f>AVERAGE(I7,I9,AVERAGE(I3,I6),I2,I4,AVERAGE(I5,I11),I8,I10,I12)</f>
+        <v>0.9984019997460829</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="5"/>
+        <v>0.38226420129528077</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -828,8 +2079,27 @@
         <f t="shared" si="3"/>
         <v>1.1319457291911112</v>
       </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <f>AVERAGE(I3,I9,I7,I8,AVERAGE(I5,I10),I2,I6,I4,I11,I12)</f>
+        <v>0.99265765871188627</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>0.19528868772509242</v>
+      </c>
+      <c r="O12">
+        <f>AVERAGE(I7,I9,I3,I6,I2,I4,AVERAGE(I5,I11),I8,I10,I12)</f>
+        <v>0.99289144880626012</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="5"/>
+        <v>0.17178274620349041</v>
+      </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I13">
         <f>AVERAGE(I2:I12)</f>
         <v>0.99460004795825629</v>
@@ -838,5 +2108,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Perf/speedup/17fp_time.xlsx
+++ b/Perf/speedup/17fp_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76255CC-0776-4B40-BC3C-73EA20E39D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6AF4EB-8259-49EC-95DD-A9D67A255B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1536,10 +1536,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>0.93047482117237845</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>0.5636149636021256</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>0.24939551408665128</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>3.5300520657157455E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0.31809802522109326</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>1.9873029302177725</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>2.3982529465432485</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>2.5915008725290738</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0.38226420129528077</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -2099,10 +2099,20 @@
         <v>0.17178274620349041</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I13">
         <f>AVERAGE(I2:I12)</f>
         <v>0.99460004795825629</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="N14">
+        <f>AVERAGE(N4:N12)</f>
+        <v>2.6352228462532725</v>
+      </c>
+      <c r="P14">
+        <f>AVERAGE(P4:P12)</f>
+        <v>0.96639030226176592</v>
       </c>
     </row>
   </sheetData>
